--- a/quizz_cine.xlsx
+++ b/quizz_cine.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
+    <sheet name="reserve" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -19,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="37">
   <si>
     <t>Niveau 1</t>
   </si>
@@ -124,6 +125,12 @@
   </si>
   <si>
     <t>Niveau 4 (Bonus)</t>
+  </si>
+  <si>
+    <t>Retour vers le Futur 2</t>
+  </si>
+  <si>
+    <t>Retour vers le Futur 3</t>
   </si>
 </sst>
 </file>
@@ -139,7 +146,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -149,12 +156,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5" tint="0.79998168889431442"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -177,10 +178,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -480,12 +481,10 @@
       <c r="D1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="E1" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="F1" s="2" t="s">
-        <v>33</v>
-      </c>
+      <c r="F1" s="2"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
@@ -508,6 +507,9 @@
       <c r="C3" s="2" t="s">
         <v>26</v>
       </c>
+      <c r="D3" s="2" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
@@ -530,41 +532,26 @@
       <c r="B5" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="C5" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>26</v>
-      </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="D6" s="2" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>8</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="C7" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="D7" s="2" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>26</v>
@@ -578,32 +565,32 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>26</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="D9" s="2" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>26</v>
       </c>
       <c r="C10" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D10" s="2" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>26</v>
@@ -617,21 +604,18 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>26</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="D12" s="2" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>26</v>
@@ -644,22 +628,19 @@
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>17</v>
+      <c r="A14" s="4" t="s">
+        <v>14</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="C14" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="D14" s="2" t="s">
+      <c r="E14" s="2" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>26</v>
@@ -673,7 +654,7 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>26</v>
@@ -687,7 +668,7 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>26</v>
@@ -701,7 +682,7 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>26</v>
@@ -715,7 +696,7 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>26</v>
@@ -729,7 +710,7 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>26</v>
@@ -743,9 +724,12 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="B21" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C21" s="2" t="s">
         <v>26</v>
       </c>
       <c r="D21" s="2" t="s">
@@ -754,21 +738,27 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>28</v>
+        <v>22</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>26</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="F22" s="2" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>29</v>
+        <v>23</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>26</v>
       </c>
       <c r="D23" s="2" t="s">
         <v>26</v>
@@ -776,9 +766,9 @@
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>30</v>
-      </c>
-      <c r="C24" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B24" s="2" t="s">
         <v>26</v>
       </c>
       <c r="D24" s="2" t="s">
@@ -787,52 +777,127 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>31</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>26</v>
-      </c>
+        <v>28</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="F25" s="2"/>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="E26" s="2" t="s">
+      <c r="A26" t="s">
+        <v>29</v>
+      </c>
+      <c r="D26" s="2" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
+        <v>30</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>31</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
         <v>32</v>
       </c>
-      <c r="E27" s="2" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A28" s="1" t="s">
+      <c r="E30" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:F5"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="24.42578125" customWidth="1"/>
+    <col min="2" max="2" width="10.42578125" style="2" customWidth="1"/>
+    <col min="3" max="4" width="9.140625" style="2"/>
+    <col min="5" max="5" width="12.28515625" style="2" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="F28" s="2" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A29" s="1" t="s">
+      <c r="F3" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="E29" s="2" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A30" s="1" t="s">
+      <c r="F4" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E30" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="F30" s="2" t="s">
+      <c r="E5" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="F5" s="2" t="s">
         <v>26</v>
       </c>
     </row>

--- a/quizz_cine.xlsx
+++ b/quizz_cine.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="39">
   <si>
     <t>Niveau 1</t>
   </si>
@@ -131,6 +131,12 @@
   </si>
   <si>
     <t>Retour vers le Futur 3</t>
+  </si>
+  <si>
+    <t>Vampire Diaries</t>
+  </si>
+  <si>
+    <t>Les Razmokets</t>
   </si>
 </sst>
 </file>
@@ -462,7 +468,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F30"/>
+  <dimension ref="A1:F32"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="24.42578125" customWidth="1"/>
@@ -628,13 +634,10 @@
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="4" t="s">
-        <v>14</v>
+      <c r="A14" t="s">
+        <v>38</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="E14" s="2" t="s">
         <v>26</v>
       </c>
     </row>
@@ -805,25 +808,41 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
+        <v>37</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
         <v>31</v>
       </c>
-      <c r="E28" s="2" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A29" s="4" t="s">
+      <c r="E29" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="E29" s="2" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
+      <c r="E30" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
         <v>32</v>
       </c>
-      <c r="E30" s="2" t="s">
+      <c r="E31" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A32" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="E32" s="2" t="s">
         <v>26</v>
       </c>
     </row>

--- a/quizz_cine.xlsx
+++ b/quizz_cine.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="67">
   <si>
     <t>Niveau 1</t>
   </si>
@@ -137,6 +137,90 @@
   </si>
   <si>
     <t>Les Razmokets</t>
+  </si>
+  <si>
+    <t>bbcm</t>
+  </si>
+  <si>
+    <t>bj</t>
+  </si>
+  <si>
+    <t>chpr</t>
+  </si>
+  <si>
+    <t>bz</t>
+  </si>
+  <si>
+    <t>dd</t>
+  </si>
+  <si>
+    <t>pw</t>
+  </si>
+  <si>
+    <t>btf</t>
+  </si>
+  <si>
+    <t>dv</t>
+  </si>
+  <si>
+    <t>etc</t>
+  </si>
+  <si>
+    <t>lk</t>
+  </si>
+  <si>
+    <t>rzm</t>
+  </si>
+  <si>
+    <t>pch</t>
+  </si>
+  <si>
+    <t>pme</t>
+  </si>
+  <si>
+    <t>rrr</t>
+  </si>
+  <si>
+    <t>shk</t>
+  </si>
+  <si>
+    <t>spk</t>
+  </si>
+  <si>
+    <t>tm</t>
+  </si>
+  <si>
+    <t>tt</t>
+  </si>
+  <si>
+    <t>tw</t>
+  </si>
+  <si>
+    <t>kk</t>
+  </si>
+  <si>
+    <t>bbcp</t>
+  </si>
+  <si>
+    <t>dshp</t>
+  </si>
+  <si>
+    <t>vp</t>
+  </si>
+  <si>
+    <t>pll</t>
+  </si>
+  <si>
+    <t>chicas</t>
+  </si>
+  <si>
+    <t>mission</t>
+  </si>
+  <si>
+    <t>ms</t>
+  </si>
+  <si>
+    <t>anna</t>
   </si>
 </sst>
 </file>
@@ -468,47 +552,50 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F32"/>
+  <dimension ref="A1:G32"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="24.42578125" customWidth="1"/>
-    <col min="2" max="2" width="10.42578125" style="2" customWidth="1"/>
-    <col min="3" max="4" width="9.140625" style="2"/>
-    <col min="5" max="5" width="12.28515625" style="2" customWidth="1"/>
+    <col min="1" max="2" width="24.42578125" customWidth="1"/>
+    <col min="3" max="3" width="10.42578125" style="2" customWidth="1"/>
+    <col min="4" max="5" width="9.140625" style="2"/>
+    <col min="6" max="6" width="12.28515625" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B1" s="2" t="s">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="D1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="E1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="F1" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="F1" s="2"/>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G1" s="2"/>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>25</v>
       </c>
-      <c r="C2" s="2" t="s">
-        <v>26</v>
+      <c r="B2" t="s">
+        <v>66</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E2" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="2" t="s">
-        <v>26</v>
+      <c r="B3" t="s">
+        <v>39</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>26</v>
@@ -517,12 +604,12 @@
         <v>26</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>26</v>
+      <c r="B4" t="s">
+        <v>40</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>26</v>
@@ -530,37 +617,49 @@
       <c r="D4" s="2" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E4" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="2" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B5" t="s">
+        <v>45</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>35</v>
       </c>
-      <c r="C6" s="2" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B6" t="s">
+        <v>45</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>36</v>
       </c>
-      <c r="D7" s="2" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B7" t="s">
+        <v>45</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="2" t="s">
-        <v>26</v>
+      <c r="B8" t="s">
+        <v>42</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>26</v>
@@ -568,24 +667,30 @@
       <c r="D8" s="2" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E8" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="2" t="s">
-        <v>26</v>
+      <c r="B9" t="s">
+        <v>41</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D9" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="2" t="s">
-        <v>26</v>
+      <c r="B10" t="s">
+        <v>43</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>26</v>
@@ -593,13 +698,16 @@
       <c r="D10" s="2" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E10" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>11</v>
       </c>
-      <c r="B11" s="2" t="s">
-        <v>26</v>
+      <c r="B11" t="s">
+        <v>46</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>26</v>
@@ -607,24 +715,30 @@
       <c r="D11" s="2" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E11" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>12</v>
       </c>
-      <c r="B12" s="2" t="s">
-        <v>26</v>
+      <c r="B12" t="s">
+        <v>47</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D12" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>13</v>
       </c>
-      <c r="B13" s="2" t="s">
-        <v>26</v>
+      <c r="B13" t="s">
+        <v>48</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>26</v>
@@ -632,21 +746,27 @@
       <c r="D13" s="2" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E13" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>38</v>
       </c>
-      <c r="B14" s="2" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B14" t="s">
+        <v>49</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>15</v>
       </c>
-      <c r="B15" s="2" t="s">
-        <v>26</v>
+      <c r="B15" t="s">
+        <v>50</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>26</v>
@@ -654,13 +774,16 @@
       <c r="D15" s="2" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E15" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>16</v>
       </c>
-      <c r="B16" s="2" t="s">
-        <v>26</v>
+      <c r="B16" t="s">
+        <v>50</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>26</v>
@@ -668,13 +791,16 @@
       <c r="D16" s="2" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E16" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>17</v>
       </c>
-      <c r="B17" s="2" t="s">
-        <v>26</v>
+      <c r="B17" t="s">
+        <v>51</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>26</v>
@@ -682,13 +808,16 @@
       <c r="D17" s="2" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E17" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>18</v>
       </c>
-      <c r="B18" s="2" t="s">
-        <v>26</v>
+      <c r="B18" t="s">
+        <v>44</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>26</v>
@@ -696,13 +825,16 @@
       <c r="D18" s="2" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E18" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>19</v>
       </c>
-      <c r="B19" s="2" t="s">
-        <v>26</v>
+      <c r="B19" t="s">
+        <v>52</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>26</v>
@@ -710,13 +842,16 @@
       <c r="D19" s="2" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E19" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>20</v>
       </c>
-      <c r="B20" s="2" t="s">
-        <v>26</v>
+      <c r="B20" t="s">
+        <v>53</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>26</v>
@@ -724,13 +859,16 @@
       <c r="D20" s="2" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E20" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>21</v>
       </c>
-      <c r="B21" s="2" t="s">
-        <v>26</v>
+      <c r="B21" t="s">
+        <v>54</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>26</v>
@@ -738,13 +876,16 @@
       <c r="D21" s="2" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E21" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>22</v>
       </c>
-      <c r="B22" s="2" t="s">
-        <v>26</v>
+      <c r="B22" t="s">
+        <v>55</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>26</v>
@@ -752,13 +893,16 @@
       <c r="D22" s="2" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E22" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>23</v>
       </c>
-      <c r="B23" s="2" t="s">
-        <v>26</v>
+      <c r="B23" t="s">
+        <v>56</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>26</v>
@@ -766,83 +910,113 @@
       <c r="D23" s="2" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E23" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>24</v>
       </c>
-      <c r="B24" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B24" t="s">
+        <v>57</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>28</v>
       </c>
-      <c r="D25" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="F25" s="2"/>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B25" t="s">
+        <v>58</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="G25" s="2"/>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>29</v>
       </c>
-      <c r="D26" s="2" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B26" t="s">
+        <v>59</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>30</v>
       </c>
-      <c r="C27" s="2" t="s">
-        <v>26</v>
+      <c r="B27" t="s">
+        <v>60</v>
       </c>
       <c r="D27" s="2" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E27" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>37</v>
       </c>
-      <c r="D28" s="2" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B28" t="s">
+        <v>61</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>31</v>
       </c>
-      <c r="E29" s="2" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B29" t="s">
+        <v>64</v>
+      </c>
+      <c r="F29" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="E30" s="2" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B30" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="F30" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>32</v>
       </c>
-      <c r="E31" s="2" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B31" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="F31" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="E32" s="2" t="s">
+      <c r="B32" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="F32" s="2" t="s">
         <v>26</v>
       </c>
     </row>

--- a/quizz_cine.xlsx
+++ b/quizz_cine.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="67">
   <si>
     <t>Niveau 1</t>
   </si>
@@ -876,9 +876,6 @@
       <c r="D21" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="E21" s="2" t="s">
-        <v>26</v>
-      </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" t="s">

--- a/quizz_cine.xlsx
+++ b/quizz_cine.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="69">
   <si>
     <t>Niveau 1</t>
   </si>
@@ -221,6 +221,12 @@
   </si>
   <si>
     <t>anna</t>
+  </si>
+  <si>
+    <t>27 robes</t>
+  </si>
+  <si>
+    <t>vsr</t>
   </si>
 </sst>
 </file>
@@ -552,7 +558,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G32"/>
+  <dimension ref="A1:G33"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="24.42578125" customWidth="1"/>
@@ -586,9 +592,6 @@
       <c r="D2" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="E2" s="2" t="s">
-        <v>26</v>
-      </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
@@ -975,45 +978,56 @@
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
+        <v>67</v>
+      </c>
+      <c r="B29" t="s">
+        <v>68</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
         <v>31</v>
       </c>
-      <c r="B29" t="s">
+      <c r="B30" t="s">
         <v>64</v>
       </c>
-      <c r="F29" s="2" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A30" s="4" t="s">
+      <c r="F30" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A31" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="B30" s="4" t="s">
+      <c r="B31" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="F30" s="2" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
+      <c r="F31" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
         <v>32</v>
       </c>
-      <c r="B31" s="4" t="s">
+      <c r="B32" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="F31" s="2" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A32" s="4" t="s">
+      <c r="F32" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A33" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="B32" s="4" t="s">
+      <c r="B33" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="F32" s="2" t="s">
+      <c r="F33" s="2" t="s">
         <v>26</v>
       </c>
     </row>
